--- a/output/pdf_financials_xlsx/JUN.A.xlsx
+++ b/output/pdf_financials_xlsx/JUN.A.xlsx
@@ -5993,10 +5993,10 @@
         <v>0.042831</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0.042831</v>
+        <v>2.181983</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0.042831</v>
+        <v>4.524495</v>
       </c>
     </row>
     <row r="93">
@@ -10248,7 +10248,11 @@
           <t>Share-based payment reserve (note 16(c))</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -10347,7 +10351,11 @@
           <t>Warrant reserve (note 16(d))</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -11548,7 +11556,11 @@
           <t>Share-based payment reserve (note 13(c))</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -11649,7 +11661,11 @@
           <t>Warrant reserve (note 13(d))</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/JUN.A.xlsx
+++ b/output/pdf_financials_xlsx/JUN.A.xlsx
@@ -7823,19 +7823,19 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.190827</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.223027</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.306018</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.369076</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.434035</v>
       </c>
     </row>
     <row r="125">
@@ -7881,19 +7881,19 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.190827</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.223027</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.306018</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.369076</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.434035</v>
       </c>
     </row>
     <row r="126">
@@ -24639,7 +24639,11 @@
           <t>Lease payments (note 14)</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -25840,7 +25844,11 @@
           <t>Lease payments (note 11)</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -34181,7 +34189,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">

--- a/output/pdf_financials_xlsx/JUN.A.xlsx
+++ b/output/pdf_financials_xlsx/JUN.A.xlsx
@@ -1376,13 +1376,13 @@
         <v>-0.253418</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>2.310502</v>
+        <v>-2.310502</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>4.159625</v>
+        <v>-4.159625</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.675176</v>
+        <v>-0.675176</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>1.947911</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-5.958467</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -7177,55 +7177,55 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-21.024123</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-88.329488</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-39.622128</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-26.468772</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-19.843601</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-9.566649</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-19.652643</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-7.545145</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-14.807789</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-20.751092</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-8.674752</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-7.357516</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-11.831774</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-1.941243</v>
       </c>
       <c r="P114" s="3" t="n">
-        <v>0</v>
+        <v>-0.10218</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0</v>
+        <v>-0.848287</v>
       </c>
       <c r="R114" s="3" t="n">
-        <v>0</v>
+        <v>-0.13409</v>
       </c>
     </row>
     <row r="115">
@@ -23329,7 +23329,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -23614,7 +23618,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -27230,7 +27238,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -32124,7 +32136,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E243" s="5" t="n">
         <v>-21.024123</v>
       </c>
@@ -43914,7 +43930,11 @@
           <t>Income tax recovery (note 13)</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -45302,7 +45322,11 @@
           <t>Income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -50011,7 +50035,11 @@
           <t>Loss from discontinued operations (note 8)</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E424" s="5" t="n">
         <v>-5.958467</v>
       </c>
